--- a/academias/Física - Estadisticos 20241.xlsx
+++ b/academias/Física - Estadisticos 20241.xlsx
@@ -744,13 +744,13 @@
         <v>35.7</v>
       </c>
       <c r="I8" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -779,10 +779,10 @@
         <v>6.8</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1012,10 +1012,10 @@
         <v>6.7</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1293,25 +1293,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>21.4</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>238</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>90.8</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>23</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>20</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>18</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>27.8</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>25</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>63</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F15">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>25.4</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>324</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F16">
-        <v>324</v>
+        <v>232</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J16">
-        <v>324</v>
+        <v>210</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>64.8</v>
       </c>
     </row>
   </sheetData>
@@ -1854,25 +1854,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>64.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>35.7</v>
+        <v>21.4</v>
       </c>
       <c r="I8" s="2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>238</v>
       </c>
       <c r="E9">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F9">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1">
-        <v>74.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>25.6</v>
+        <v>23.9</v>
       </c>
       <c r="I9" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         <v>20</v>
       </c>
       <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12">
         <v>8</v>
       </c>
-      <c r="F12">
-        <v>12</v>
-      </c>
       <c r="G12" s="1">
+        <v>60</v>
+      </c>
+      <c r="H12" s="1">
         <v>40</v>
       </c>
-      <c r="H12" s="1">
-        <v>60</v>
-      </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>18</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>55.6</v>
+        <v>72.2</v>
       </c>
       <c r="H13" s="1">
-        <v>44.4</v>
+        <v>27.8</v>
       </c>
       <c r="I13" s="2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2058,19 +2058,19 @@
         <v>25</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H14" s="1">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>63</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1">
-        <v>54</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>46</v>
+        <v>25.4</v>
       </c>
       <c r="I15" s="2">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2119,25 +2119,25 @@
         <v>324</v>
       </c>
       <c r="E16">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="F16">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G16" s="1">
-        <v>72.2</v>
+        <v>77.5</v>
       </c>
       <c r="H16" s="1">
-        <v>27.8</v>
+        <v>22.5</v>
       </c>
       <c r="I16" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20241.xlsx
+++ b/academias/Física - Estadisticos 20241.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="29">
   <si>
     <t>Docente</t>
   </si>
@@ -51,15 +51,18 @@
     <t>por_blancos</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
+    <t>Martínez Sota Luis Rey</t>
+  </si>
+  <si>
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
+    <t>Urias Morales Alejandra</t>
+  </si>
+  <si>
     <t>FÍSICA II</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
     <t>Totales Generales</t>
   </si>
   <si>
+    <t>5ARHV</t>
+  </si>
+  <si>
     <t>5AEM</t>
   </si>
   <si>
@@ -87,19 +93,16 @@
     <t>5BLCM</t>
   </si>
   <si>
+    <t>5AEV</t>
+  </si>
+  <si>
+    <t>5APV</t>
+  </si>
+  <si>
+    <t>5ASV</t>
+  </si>
+  <si>
     <t>5ALCV</t>
-  </si>
-  <si>
-    <t>5ARHV</t>
-  </si>
-  <si>
-    <t>5AEV</t>
-  </si>
-  <si>
-    <t>5APV</t>
-  </si>
-  <si>
-    <t>5ASV</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -513,28 +516,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>67.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -548,28 +551,25 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -580,31 +580,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>79.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>20.6</v>
+        <v>32.1</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -615,31 +615,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>67.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>32.5</v>
+        <v>14.6</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -650,28 +650,28 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>64.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>35.5</v>
+        <v>20.6</v>
       </c>
       <c r="I6" s="2">
         <v>6.7</v>
@@ -685,31 +685,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>86.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H7" s="1">
-        <v>13.9</v>
+        <v>32.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -720,31 +720,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="H8" s="1">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="I8" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -755,28 +755,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
       <c r="D9">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>177</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>74.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>25.6</v>
+        <v>13.9</v>
       </c>
       <c r="I9" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -790,28 +793,25 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1">
-        <v>100</v>
+        <v>75.7</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -822,28 +822,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
       <c r="D11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -857,28 +860,28 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
         <v>8</v>
       </c>
-      <c r="F12">
-        <v>12</v>
-      </c>
       <c r="G12" s="1">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="H12" s="1">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="I12" s="2">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -892,28 +895,28 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>55.6</v>
+        <v>64</v>
       </c>
       <c r="H13" s="1">
-        <v>44.4</v>
+        <v>36</v>
       </c>
       <c r="I13" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -927,28 +930,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H14" s="1">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I14" s="2">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -959,28 +959,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
       <c r="D15">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>54</v>
+        <v>64.3</v>
       </c>
       <c r="H15" s="1">
-        <v>46</v>
+        <v>35.7</v>
       </c>
       <c r="I15" s="2">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -990,31 +993,63 @@
       </c>
     </row>
     <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>18</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>64.3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>35.7</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
         <v>324</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>234</v>
       </c>
-      <c r="F16">
+      <c r="F17">
         <v>90</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" s="1">
         <v>72.2</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H17" s="1">
         <v>27.8</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I17" s="2">
         <v>6.7</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1025,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1074,34 +1109,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1109,54 +1144,51 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1168,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1176,22 +1208,22 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1203,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1211,22 +1243,22 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1238,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1246,22 +1278,22 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1273,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1281,69 +1313,72 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
-        <v>78.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>21.4</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
       <c r="D9">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>90.8</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="K9" s="1">
-        <v>88.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1351,60 +1386,60 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>100</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
       <c r="D11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1418,28 +1453,28 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>72.2</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1453,28 +1488,28 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>72.2</v>
+        <v>88</v>
       </c>
       <c r="H13" s="1">
-        <v>27.8</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1488,28 +1523,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E14">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>88</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>12</v>
+        <v>25.4</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1520,28 +1552,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
       <c r="D15">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>74.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>25.4</v>
+        <v>21.4</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1551,31 +1586,63 @@
       </c>
     </row>
     <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16" s="1">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="H16" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
         <v>324</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>92</v>
       </c>
-      <c r="F16">
+      <c r="F17">
         <v>232</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" s="1">
         <v>28.4</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H17" s="1">
         <v>71.59999999999999</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I17" s="2">
         <v>3.7</v>
       </c>
-      <c r="J16">
+      <c r="J17">
         <v>210</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K17" s="1">
         <v>64.8</v>
       </c>
     </row>
@@ -1586,7 +1653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1635,28 +1702,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>67.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1670,28 +1737,25 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1702,31 +1766,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>79.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>20.6</v>
+        <v>32.1</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1737,31 +1801,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>67.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>32.5</v>
+        <v>14.6</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1772,28 +1836,28 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>64.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>35.5</v>
+        <v>20.6</v>
       </c>
       <c r="I6" s="2">
         <v>6.7</v>
@@ -1807,31 +1871,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>86.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H7" s="1">
-        <v>13.9</v>
+        <v>32.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1842,31 +1906,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>78.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="H8" s="1">
-        <v>21.4</v>
+        <v>35.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1877,28 +1941,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
       <c r="D9">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>76.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>23.9</v>
+        <v>13.9</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1912,28 +1979,25 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1">
-        <v>100</v>
+        <v>75.7</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="I10" s="2">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1944,28 +2008,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
       <c r="D11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1979,28 +2046,28 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>72.2</v>
       </c>
       <c r="H12" s="1">
-        <v>40</v>
+        <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2014,28 +2081,28 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>72.2</v>
+        <v>88</v>
       </c>
       <c r="H13" s="1">
-        <v>27.8</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2049,28 +2116,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E14">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>88</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>12</v>
+        <v>25.4</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2081,25 +2145,28 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
       <c r="D15">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>74.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>25.4</v>
+        <v>21.4</v>
       </c>
       <c r="I15" s="2">
         <v>7.1</v>
@@ -2112,31 +2179,63 @@
       </c>
     </row>
     <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16" s="1">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="H16" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
         <v>324</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>251</v>
       </c>
-      <c r="F16">
+      <c r="F17">
         <v>73</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" s="1">
         <v>77.5</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H17" s="1">
         <v>22.5</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I17" s="2">
         <v>7.2</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Física - Estadisticos 20241.xlsx
+++ b/academias/Física - Estadisticos 20241.xlsx
@@ -1185,25 +1185,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>210</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="F10">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1625,25 +1625,25 @@
         <v>324</v>
       </c>
       <c r="E17">
-        <v>92</v>
+        <v>279</v>
       </c>
       <c r="F17">
-        <v>232</v>
+        <v>45</v>
       </c>
       <c r="G17" s="1">
-        <v>28.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>71.59999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="I17" s="2">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>64.8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1778,19 +1778,19 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>67.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>32.1</v>
+        <v>17.9</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1813,19 +1813,19 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>85.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H5" s="1">
-        <v>14.6</v>
+        <v>7.3</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1848,19 +1848,19 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>79.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H6" s="1">
-        <v>20.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1883,19 +1883,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>67.5</v>
+        <v>80</v>
       </c>
       <c r="H7" s="1">
-        <v>32.5</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1918,19 +1918,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>64.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>35.5</v>
+        <v>12.9</v>
       </c>
       <c r="I8" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1953,19 +1953,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>86.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1985,19 +1985,19 @@
         <v>210</v>
       </c>
       <c r="E10">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="F10">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1">
-        <v>75.7</v>
+        <v>89</v>
       </c>
       <c r="H10" s="1">
-        <v>24.3</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>324</v>
       </c>
       <c r="E17">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="F17">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G17" s="1">
-        <v>77.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>22.5</v>
+        <v>13.9</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Física - Estadisticos 20241.xlsx
+++ b/academias/Física - Estadisticos 20241.xlsx
@@ -522,28 +522,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I2" s="2">
         <v>8.5</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -554,28 +554,28 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I3" s="2">
         <v>8.5</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -589,28 +589,28 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>19</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>67.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="H4" s="1">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="I4" s="2">
         <v>6.9</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -694,28 +694,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>27</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>67.5</v>
+        <v>61.4</v>
       </c>
       <c r="H7" s="1">
-        <v>32.5</v>
+        <v>38.6</v>
       </c>
       <c r="I7" s="2">
         <v>6.6</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -796,28 +796,28 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E10">
         <v>159</v>
       </c>
       <c r="F10">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1">
-        <v>75.7</v>
+        <v>74</v>
       </c>
       <c r="H10" s="1">
-        <v>24.3</v>
+        <v>26</v>
       </c>
       <c r="I10" s="2">
         <v>6.9</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -831,28 +831,28 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="H11" s="1">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="I11" s="2">
         <v>5.3</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -901,28 +901,28 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>16</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13" s="1">
-        <v>64</v>
+        <v>55.2</v>
       </c>
       <c r="H13" s="1">
-        <v>36</v>
+        <v>44.8</v>
       </c>
       <c r="I13" s="2">
         <v>6.1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -933,28 +933,28 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E14">
         <v>34</v>
       </c>
       <c r="F14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H14" s="1">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I14" s="2">
         <v>5.8</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1029,28 +1029,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E17">
         <v>234</v>
       </c>
       <c r="F17">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G17" s="1">
-        <v>72.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>27.8</v>
+        <v>30.1</v>
       </c>
       <c r="I17" s="2">
         <v>6.7</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1115,28 +1115,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I2" s="2">
         <v>9</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1147,28 +1147,28 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I3" s="2">
         <v>9</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1182,28 +1182,28 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>23</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H4" s="1">
-        <v>17.9</v>
+        <v>20.7</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1287,28 +1287,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>32</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>27.3</v>
       </c>
       <c r="I7" s="2">
         <v>7.4</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1389,28 +1389,28 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E10">
         <v>187</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H10" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1424,28 +1424,28 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11">
         <v>12</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="H11" s="1">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="I11" s="2">
         <v>7.6</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1494,28 +1494,28 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>22</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>88</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>12</v>
+        <v>24.1</v>
       </c>
       <c r="I13" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1526,28 +1526,28 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E14">
         <v>47</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G14" s="1">
-        <v>74.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>25.4</v>
+        <v>30.9</v>
       </c>
       <c r="I14" s="2">
         <v>8</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1622,28 +1622,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E17">
         <v>279</v>
       </c>
       <c r="F17">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G17" s="1">
-        <v>86.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H17" s="1">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="I17" s="2">
         <v>8</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1708,28 +1708,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I2" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1740,28 +1740,28 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1775,28 +1775,28 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>23</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="H4" s="1">
-        <v>17.9</v>
+        <v>20.7</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1880,28 +1880,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>32</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>27.3</v>
       </c>
       <c r="I7" s="2">
         <v>7.3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1982,28 +1982,28 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E10">
         <v>187</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H10" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I10" s="2">
         <v>7.6</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2017,28 +2017,28 @@
         <v>25</v>
       </c>
       <c r="D11">
+        <v>21</v>
+      </c>
+      <c r="E11">
         <v>20</v>
       </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
       <c r="F11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>60</v>
+        <v>95.2</v>
       </c>
       <c r="H11" s="1">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2055,19 +2055,19 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2087,28 +2087,28 @@
         <v>27</v>
       </c>
       <c r="D13">
+        <v>29</v>
+      </c>
+      <c r="E13">
         <v>25</v>
       </c>
-      <c r="E13">
-        <v>22</v>
-      </c>
       <c r="F13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>88</v>
+        <v>86.2</v>
       </c>
       <c r="H13" s="1">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2119,28 +2119,28 @@
         <v>16</v>
       </c>
       <c r="D14">
+        <v>68</v>
+      </c>
+      <c r="E14">
         <v>63</v>
       </c>
-      <c r="E14">
-        <v>47</v>
-      </c>
       <c r="F14">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>74.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>25.4</v>
+        <v>7.4</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2157,19 +2157,19 @@
         <v>28</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>21.4</v>
+        <v>17.9</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>28</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>21.4</v>
+        <v>17.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2215,28 +2215,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E17">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="F17">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G17" s="1">
-        <v>86.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>13.9</v>
+        <v>11.6</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20241.xlsx
+++ b/academias/Física - Estadisticos 20241.xlsx
@@ -525,25 +525,25 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>8.5</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -557,25 +557,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
         <v>8.5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -592,25 +592,25 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>65.5</v>
+        <v>69</v>
       </c>
       <c r="H4" s="1">
-        <v>34.5</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -697,25 +697,25 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>61.4</v>
+        <v>70.5</v>
       </c>
       <c r="H7" s="1">
-        <v>38.6</v>
+        <v>29.5</v>
       </c>
       <c r="I7" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -799,25 +799,25 @@
         <v>215</v>
       </c>
       <c r="E10">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F10">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1">
-        <v>74</v>
+        <v>76.3</v>
       </c>
       <c r="H10" s="1">
-        <v>26</v>
+        <v>23.7</v>
       </c>
       <c r="I10" s="2">
         <v>6.9</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -834,25 +834,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>38.1</v>
+        <v>42.9</v>
       </c>
       <c r="H11" s="1">
-        <v>61.9</v>
+        <v>57.1</v>
       </c>
       <c r="I11" s="2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -904,25 +904,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>55.2</v>
+        <v>69</v>
       </c>
       <c r="H13" s="1">
-        <v>44.8</v>
+        <v>31</v>
       </c>
       <c r="I13" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -936,25 +936,25 @@
         <v>68</v>
       </c>
       <c r="E14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
-        <v>50</v>
+        <v>57.4</v>
       </c>
       <c r="H14" s="1">
-        <v>50</v>
+        <v>42.6</v>
       </c>
       <c r="I14" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1032,25 +1032,25 @@
         <v>335</v>
       </c>
       <c r="E17">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="F17">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G17" s="1">
-        <v>69.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>30.1</v>
+        <v>26.9</v>
       </c>
       <c r="I17" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1118,25 +1118,25 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1150,25 +1150,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
         <v>9</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>79.3</v>
+        <v>82.8</v>
       </c>
       <c r="H4" s="1">
-        <v>20.7</v>
+        <v>17.2</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="H7" s="1">
-        <v>27.3</v>
+        <v>18.2</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>215</v>
       </c>
       <c r="E10">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1">
-        <v>87</v>
+        <v>89.3</v>
       </c>
       <c r="H10" s="1">
-        <v>13</v>
+        <v>10.7</v>
       </c>
       <c r="I10" s="2">
         <v>8</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>57.1</v>
+        <v>61.9</v>
       </c>
       <c r="H11" s="1">
-        <v>42.9</v>
+        <v>38.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>75.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="H13" s="1">
-        <v>24.1</v>
+        <v>10.3</v>
       </c>
       <c r="I13" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>68</v>
       </c>
       <c r="E14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>69.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="H14" s="1">
-        <v>30.9</v>
+        <v>23.5</v>
       </c>
       <c r="I14" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1625,25 +1625,25 @@
         <v>335</v>
       </c>
       <c r="E17">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F17">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G17" s="1">
-        <v>83.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="I17" s="2">
         <v>8</v>
       </c>
       <c r="J17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1711,25 +1711,25 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>8.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1743,25 +1743,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
         <v>8.9</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1778,25 +1778,25 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>20.7</v>
+        <v>6.9</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1813,19 +1813,19 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>92.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1848,16 +1848,16 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="2">
         <v>7.6</v>
@@ -1883,25 +1883,25 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>72.7</v>
+        <v>77.3</v>
       </c>
       <c r="H7" s="1">
-        <v>27.3</v>
+        <v>22.7</v>
       </c>
       <c r="I7" s="2">
         <v>7.3</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1918,19 +1918,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>87.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H8" s="1">
-        <v>12.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1985,25 +1985,25 @@
         <v>215</v>
       </c>
       <c r="E10">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>87</v>
+        <v>91.2</v>
       </c>
       <c r="H10" s="1">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="2">
         <v>7.6</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2020,25 +2020,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2090,25 +2090,25 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2122,25 +2122,25 @@
         <v>68</v>
       </c>
       <c r="E14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2218,25 +2218,25 @@
         <v>335</v>
       </c>
       <c r="E17">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="F17">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1">
-        <v>88.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="H17" s="1">
-        <v>11.6</v>
+        <v>7.2</v>
       </c>
       <c r="I17" s="2">
         <v>7.7</v>
       </c>
       <c r="J17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
